--- a/data/processed_data/Video_prueba/serie_temporal.xlsx
+++ b/data/processed_data/Video_prueba/serie_temporal.xlsx
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>294.3510544610874</v>
+        <v>294.3510544610875</v>
       </c>
     </row>
     <row r="3">
@@ -611,7 +611,7 @@
         <v>0.015</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>294.3017789928648</v>
+        <v>294.3017789928649</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         <v>0.04666666666666667</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>294.2473584446553</v>
+        <v>294.2473584446554</v>
       </c>
     </row>
     <row r="5">
@@ -697,7 +697,7 @@
         <v>0.07166666666666667</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>294.1917544422002</v>
+        <v>294.1917544422003</v>
       </c>
     </row>
     <row r="6">
@@ -740,7 +740,7 @@
         <v>0.105</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>294.1389286112408</v>
+        <v>294.1389286112409</v>
       </c>
     </row>
     <row r="7">
@@ -86654,7 +86654,7 @@
         <v>67.33666666666667</v>
       </c>
       <c r="M2004" s="2" t="n">
-        <v>294.1629141057251</v>
+        <v>294.162914105725</v>
       </c>
     </row>
     <row r="2005">
@@ -86740,7 +86740,7 @@
         <v>67.40333333333334</v>
       </c>
       <c r="M2006" s="2" t="n">
-        <v>294.1544857181056</v>
+        <v>294.1544857181057</v>
       </c>
     </row>
     <row r="2007">
@@ -86783,7 +86783,7 @@
         <v>67.44</v>
       </c>
       <c r="M2007" s="2" t="n">
-        <v>294.1523969775474</v>
+        <v>294.1523969775477</v>
       </c>
     </row>
     <row r="2008">
@@ -86826,7 +86826,7 @@
         <v>67.47500000000001</v>
       </c>
       <c r="M2008" s="2" t="n">
-        <v>294.1529414842681</v>
+        <v>294.1529414842684</v>
       </c>
     </row>
   </sheetData>
@@ -86841,7 +86841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -87242,6 +87242,36 @@
         <v>0.7989000000000001</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde sup (px)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.107</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde inf (px)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0.862</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo peor / grosor (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.376</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
